--- a/reisemu-de/spanien/semantics-spanien.xlsx
+++ b/reisemu-de/spanien/semantics-spanien.xlsx
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ключі'!$A$1:$N$87</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Кластери'!$A$1:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Кластери'!$A$1:$L$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Типи посадкових конкурентів'!$A$1:$G$736</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Матриця типів по ключах'!$A$1:$T$87</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Напрямки розширення'!$A$1:$G$13</definedName>
@@ -558,25 +558,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>38380</v>
+        <v>35340</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K01a, K04a, K05a, K06</t>
+          <t>K01a, K05a, K06</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>інше: 154/477 (32%)</t>
+          <t>хаб країни: 145/456 (32%)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Кілька кластерів (K01a, K04a, K05a, K06) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Хаб країни «Spanien»: у ТОП домінують хаби країни.</t>
+          <t>Кілька кластерів (K01a, K05a, K06) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Хаб країни «Spanien»: у ТОП домінують хаби країни.</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/malaga</t>
+          <t>https://reisemu.de/hotels/spanien</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -664,66 +664,66 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>640</v>
+        <v>3200</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>K07</t>
+          <t>K04, K01b</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>хаб регіону: 13/18 (72%)</t>
+          <t>інше: 12/37 (32%)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Один кластер — одна сторінка. </t>
+          <t>Кілька кластерів (K04, K01b) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Хаб готелів.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/reisehinweise</t>
+          <t>https://reisemu.de/tour/spanien/malaga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>нова</t>
+          <t>існує</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>K08, K16</t>
+          <t>K07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>інформаційна: 13/18 (72%)</t>
+          <t>хаб регіону: 13/18 (72%)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Кілька кластерів (K08, K16) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
+          <t xml:space="preserve">Один кластер — одна сторінка. </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/rundreisen</t>
+          <t>https://reisemu.de/tour/spanien/reisehinweise</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -732,32 +732,32 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>390</v>
+        <v>660</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>K05b</t>
+          <t>K08, K16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rundreise: 6/9 (67%)</t>
+          <t>інформаційна: 13/18 (72%)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Один кластер — одна сторінка. Rundreise — інший продукт (тури з маршрутом).</t>
+          <t>Кілька кластерів (K08, K16) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/last-minute</t>
+          <t>https://reisemu.de/tour/spanien/rundreisen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -773,46 +773,46 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>K09</t>
+          <t>K05b</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>last minute (країна): 6/9 (67%)</t>
+          <t>rundreise: 6/9 (67%)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Один кластер — одна сторінка. </t>
+          <t>Один кластер — одна сторінка. Rundreise — інший продукт (тури з маршрутом).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/alicante</t>
+          <t>https://reisemu.de/tour/spanien/last-minute</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>існує</t>
+          <t>нова</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>K10</t>
+          <t>K09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>хаб регіону: 4/9 (44%)</t>
+          <t>last minute (країна): 6/9 (67%)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -825,7 +825,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/mallorca</t>
+          <t>https://reisemu.de/tour/spanien/alicante</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>K11</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>хаб регіону: 6/8 (75%)</t>
+          <t>хаб регіону: 4/9 (44%)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/valencia</t>
+          <t>https://reisemu.de/tour/spanien/mallorca</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -871,16 +871,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>K12</t>
+          <t>K11</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>хаб регіону: 9/18 (50%)</t>
+          <t>хаб регіону: 6/8 (75%)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -893,7 +893,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/andalusien</t>
+          <t>https://reisemu.de/tour/spanien/valencia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -905,16 +905,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>K13</t>
+          <t>K12</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>rundreise: 3/8 (38%)</t>
+          <t>хаб регіону: 9/18 (50%)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
@@ -927,7 +927,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/barcelona</t>
+          <t>https://reisemu.de/tour/spanien/andalusien</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>K14</t>
+          <t>K13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>хаб регіону: 8/10 (80%)</t>
+          <t>rundreise: 3/8 (38%)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -961,7 +961,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/october</t>
+          <t>https://reisemu.de/tour/spanien/barcelona</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -973,29 +973,29 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>K15</t>
+          <t>K14</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>хаб країни: 4/8 (50%)</t>
+          <t>хаб регіону: 8/10 (80%)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Один кластер — одна сторінка. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
+          <t xml:space="preserve">Один кластер — одна сторінка. </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://reisemu.de/hotels/spanien</t>
+          <t>https://reisemu.de/tour/spanien/october</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>K01b, K04b</t>
+          <t>K15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>готель: 10/16 (62%)</t>
+          <t>хаб країни: 4/8 (50%)</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Кілька кластерів (K01b, K04b) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Хаб готелів.</t>
+          <t>Один кластер — одна сторінка. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
         </is>
       </c>
     </row>
@@ -5874,27 +5874,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>spanien unterkunft</t>
+          <t>ferien in spanien 2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>житло в Іспанії</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>канікули в Іспанії 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>імовірно дати шкільних канікул</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.120000004768372</v>
+        <v>1.14</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5909,22 +5913,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (4/7)</t>
+          <t>найкращий кандидат: /tour/spanien (0/7). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -5936,23 +5940,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>unterkünfte spanien</t>
+          <t>kurztrip spanien</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>варіанти житла в Іспанії</t>
+          <t>коротка поїздка до Іспанії</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.120000004768372</v>
+        <v>0.8100000023841858</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -5971,22 +5975,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (2/7)</t>
+          <t>найкращий кандидат: /tour/spanien (6/9)</t>
         </is>
       </c>
     </row>
@@ -5998,31 +6002,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ferien in spanien 2026</t>
+          <t>spanien urlaub inseln</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>канікули в Іспанії 2026</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>імовірно дати шкільних канікул</t>
-        </is>
-      </c>
+          <t>відпочинок на островах Іспанії</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1.14</v>
+        <v>0.89</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6037,22 +6037,22 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (0/7). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (3/8)</t>
         </is>
       </c>
     </row>
@@ -6064,23 +6064,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kurztrip spanien</t>
+          <t>spanien insel urlaub</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>коротка поїздка до Іспанії</t>
+          <t>відпочинок на острові в Іспанії</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8100000023841858</v>
+        <v>0.89</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -6099,22 +6099,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (6/9)</t>
+          <t>найкращий кандидат: /tour/spanien (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -6126,12 +6126,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>spanien urlaub inseln</t>
+          <t>schöne urlaubsorte spanien</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>відпочинок на островах Іспанії</t>
+          <t>гарні курорти Іспанії</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -6142,11 +6142,11 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.89</v>
+        <v>0.9800000190734863</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -6188,27 +6188,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>spanien insel urlaub</t>
+          <t>spain holiday</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>відпочинок на острові в Іспанії</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>відпочинок в Іспанії</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>англійською</t>
+        </is>
+      </c>
       <c r="E27" t="n">
         <v>210</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G27" t="n">
-        <v>0.89</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6223,12 +6227,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>готель</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -6238,7 +6242,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (0/8). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -6250,23 +6254,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>schöne urlaubsorte spanien</t>
+          <t>spain holidays</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>гарні курорти Іспанії</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
+          <t>відпочинок в Іспанії</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>англійською; також «свята в Іспанії»</t>
+        </is>
+      </c>
       <c r="E28" t="n">
         <v>210</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9800000190734863</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -6285,12 +6293,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -6300,7 +6308,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (3/8)</t>
+          <t>найкращий кандидат: /tour/spanien (4/9)</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6320,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>spain holiday</t>
+          <t>spanien holiday</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6322,14 +6330,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>англійською</t>
+          <t>суміш німецької й англійської</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>210</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G29" t="n">
         <v>1.059999942779541</v>
@@ -6351,22 +6359,22 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>готель</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (0/8). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien (5/9)</t>
         </is>
       </c>
     </row>
@@ -6378,27 +6386,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>spain holidays</t>
+          <t>spanien schönste urlaubsorte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>англійською; також «свята в Іспанії»</t>
-        </is>
-      </c>
+          <t>найкращі курорти Іспанії</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" t="n">
         <v>210</v>
       </c>
       <c r="F30" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.059999942779541</v>
+        <v>0.9800000190734863</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -6417,7 +6421,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -6432,7 +6436,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (4/9)</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (4/9)</t>
         </is>
       </c>
     </row>
@@ -6444,31 +6448,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>spanien holiday</t>
+          <t>spanien familienurlaub</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>суміш німецької й англійської</t>
-        </is>
-      </c>
+          <t>сімейний відпочинок в Іспанії</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.059999942779541</v>
+        <v>0.9800000190734863</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -6488,17 +6488,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (5/9)</t>
+          <t>найкращий кандидат: /tour/spanien (4/9)</t>
         </is>
       </c>
     </row>
@@ -6510,27 +6510,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>spanien schönste urlaubsorte</t>
+          <t>spanien urlaub am meer mit flug</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>найкращі курорти Іспанії</t>
+          <t>відпочинок на морі в Іспанії з перельотом</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9800000190734863</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (4/9)</t>
+          <t>найкращий кандидат: /tour/spanien (3/9)</t>
         </is>
       </c>
     </row>
@@ -6572,27 +6572,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>spanien familienurlaub</t>
+          <t>spanien festland urlaub am meer</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>сімейний відпочинок в Іспанії</t>
+          <t>відпочинок на морі в материковій Іспанії</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9800000190734863</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -6607,22 +6607,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (4/9)</t>
+          <t>найкращий кандидат: /tour/spanien/pauschalreise (0/8). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -6634,23 +6634,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>spanien urlaub am meer mit flug</t>
+          <t>spanien urlaub mit auto</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>відпочинок на морі в Іспанії з перельотом</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>відпочинок в Іспанії на авто</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>поїздка власним авто</t>
+        </is>
+      </c>
       <c r="E34" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.949999988079071</v>
+        <v>0.38</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -6669,22 +6673,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (3/9)</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (0/8). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -6696,27 +6700,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>spanien festland urlaub am meer</t>
+          <t>spanien urlaub am meer flug und hotel</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>відпочинок на морі в материковій Іспанії</t>
+          <t>відпочинок на морі в Іспанії: переліт і готель</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -6731,22 +6735,22 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/pauschalreise (0/8). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien (5/9)</t>
         </is>
       </c>
     </row>
@@ -6758,19 +6762,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>spanien urlaub mit auto</t>
+          <t>spanien festland urlaub strand</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії на авто</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>поїздка власним авто</t>
-        </is>
-      </c>
+          <t>пляжний відпочинок у материковій Іспанії</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" t="n">
         <v>90</v>
       </c>
@@ -6778,11 +6778,11 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -6802,17 +6802,17 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>окрема сторінка не потрібна</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (0/8). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (2/8)</t>
         </is>
       </c>
     </row>
@@ -6824,27 +6824,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>spanien urlaub am meer flug und hotel</t>
+          <t>ferien spanien 2026 sommer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>відпочинок на морі в Іспанії: переліт і готель</t>
+          <t>літні канікули в Іспанії 2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.91</v>
+        <v>15</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -6859,22 +6856,22 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>6/10</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>окрема сторінка не потрібна</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (5/9)</t>
+          <t>найкращий кандидат: /tour/spanien (2/10)</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6883,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>spanien festland urlaub strand</t>
+          <t>strandurlaub spanien festland</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6896,17 +6893,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.63</v>
+        <v>1.37</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -6921,22 +6918,22 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (2/8)</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (5/8). /ratgeber не створюємо: ключ на хаб (секція Festland / FAQ) За ТОП було б: /tour/spanien/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -6948,24 +6945,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ferien spanien 2026 sommer</t>
+          <t>kurzurlaub spanien mit flug</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>літні канікули в Іспанії 2026</t>
+          <t>короткий відпочинок в Іспанії з перельотом</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.8299999833106995</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -6980,22 +6980,22 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6/10</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (2/10)</t>
+          <t>найкращий кандидат: /tour/spanien (4/9)</t>
         </is>
       </c>
     </row>
@@ -7007,23 +7007,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>strandurlaub spanien festland</t>
+          <t>spanien hotel und flug am meer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>пляжний відпочинок у материковій Іспанії</t>
+          <t>Іспанія: готель на морі з перельотом</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1.37</v>
+        <v>0.78</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -7042,22 +7042,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>за рішенням власника</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (5/8). /ratgeber не створюємо: ключ на хаб (секція Festland / FAQ) За ТОП було б: /tour/spanien/ratgeber (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/spanien (4/9)</t>
         </is>
       </c>
     </row>
@@ -7069,27 +7069,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kurzurlaub spanien mit flug</t>
+          <t>ferien spanien 2027</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>короткий відпочинок в Іспанії з перельотом</t>
+          <t>канікули в Іспанії 2027</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" t="n">
         <v>50</v>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8299999833106995</v>
+        <v>0.86</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -7104,22 +7106,22 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>окрема сторінка не потрібна</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (4/9)</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (2/9)</t>
         </is>
       </c>
     </row>
@@ -7131,27 +7133,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>spanien hotel und flug am meer</t>
+          <t>party spanien festland</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Іспанія: готель на морі з перельотом</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>тусовочний відпочинок у материковій Іспанії</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>курорти з нічним життям</t>
+        </is>
+      </c>
       <c r="E42" t="n">
         <v>50</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.78</v>
-      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -7166,56 +7169,54 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>окрема сторінка не потрібна</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (4/9)</t>
+          <t>найкращий кандидат: /tour/spanien (2/9)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K01a · spanien urlaub</t>
+          <t>K02 · pauschalreise spanien</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ferien spanien 2027</t>
+          <t>pauschalreise spanien</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>канікули в Іспанії 2027</t>
+          <t>пакетний тур до Іспанії</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>50</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+        <v>1900</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.86</v>
+        <v>1.44</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -7225,60 +7226,63 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien</t>
+          <t>https://reisemu.de/tour/spanien/pauschalreise</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (2/9)</t>
+          <t>найкращий кандидат: /tour/spanien/pauschalreise (8/9)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>K01a · spanien urlaub</t>
+          <t>K02 · pauschalreise spanien</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>party spanien festland</t>
+          <t>pauschalreise südspanien</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>тусовочний відпочинок у материковій Іспанії</t>
+          <t>пакетний тур на південь Іспанії</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>курорти з нічним життям</t>
+          <t>Südspanien — Андалусія, Коста-дель-Соль</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>50</v>
+        <v>1900</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
+      <c r="G44" t="n">
+        <v>1.440000057220459</v>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -7288,27 +7292,27 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien</t>
+          <t>https://reisemu.de/tour/spanien/pauschalreise</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (2/9)</t>
+          <t>найкращий кандидат: /tour/spanien/pauschalreise (8/9)</t>
         </is>
       </c>
     </row>
@@ -7320,23 +7324,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pauschalreise spanien</t>
+          <t>pauschalreise spanien festland</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>пакетний тур до Іспанії</t>
+          <t>пакетний тур до материкової Іспанії</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>1900</v>
+        <v>320</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -7360,7 +7364,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -7370,7 +7374,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/pauschalreise (8/9)</t>
+          <t>найкращий кандидат: /tour/spanien/pauschalreise (5/9)</t>
         </is>
       </c>
     </row>
@@ -7382,27 +7386,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pauschalreise südspanien</t>
+          <t>pauschalreise spanien all inclusive</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>пакетний тур на південь Іспанії</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Südspanien — Андалусія, Коста-дель-Соль</t>
-        </is>
-      </c>
+          <t>пакетний тур до Іспанії «все включено»</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1900</v>
+        <v>140</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.440000057220459</v>
+        <v>1.39</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -7421,22 +7421,22 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>all inclusive (країна)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/pauschalreise (8/9)</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (5/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/spanien/pauschalreise. У ТОП pauschal-сторінок 1/9; за ТОП було б: /tour/spanien/all-inclusive (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -7448,23 +7448,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pauschalreise spanien festland</t>
+          <t>pauschalreise spanien günstig</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>пакетний тур до материкової Іспанії</t>
+          <t>недорогий пакетний тур до Іспанії</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -7510,23 +7510,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pauschalreise spanien all inclusive</t>
+          <t>spanien pauschalreisen all inclusive günstig</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>пакетний тур до Іспанії «все включено»</t>
+          <t>недорогі пакетні тури до Іспанії «все включено»</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.39</v>
+        <v>0.7</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (5/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/spanien/pauschalreise. У ТОП pauschal-сторінок 1/9; за ТОП було б: /tour/spanien/all-inclusive (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (3/7). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/spanien/pauschalreise. У ТОП pauschal-сторінок 1/7; за ТОП було б: /tour/spanien (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
@@ -7572,23 +7572,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pauschalreise spanien günstig</t>
+          <t>spanien urlaub pauschalreise</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>недорогий пакетний тур до Іспанії</t>
+          <t>пакетний тур на відпочинок до Іспанії</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -7622,35 +7622,35 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/pauschalreise (5/9)</t>
+          <t>найкращий кандидат: /tour/spanien/pauschalreise (8/9)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>K02 · pauschalreise spanien</t>
+          <t>K03 · spanien all inclusive urlaub</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>spanien pauschalreisen all inclusive günstig</t>
+          <t>spanien all inclusive urlaub</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>недорогі пакетні тури до Іспанії «все включено»</t>
+          <t>відпочинок в Іспанії «все включено»</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>70</v>
+        <v>1600</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7</v>
+        <v>1.11</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/pauschalreise</t>
+          <t>https://reisemu.de/tour/spanien/all-inclusive</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7674,45 +7674,45 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>спірно → підтверджено перевіркою</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (3/7). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/spanien/pauschalreise. У ТОП pauschal-сторінок 1/7; за ТОП було б: /tour/spanien (спірно (не перевірено)).</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (4/7). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>K02 · pauschalreise spanien</t>
+          <t>K03 · spanien all inclusive urlaub</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>spanien urlaub pauschalreise</t>
+          <t>spanien urlaub all inclusive mit flug 2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>пакетний тур на відпочинок до Іспанії</t>
+          <t>відпочинок в Іспанії «все включено» з перельотом 2026</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -7726,27 +7726,27 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/pauschalreise</t>
+          <t>https://reisemu.de/tour/spanien/all-inclusive</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>all inclusive (регіон)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно → підтверджено перевіркою</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/pauschalreise (8/9)</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (4/7). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
         </is>
       </c>
     </row>
@@ -7758,23 +7758,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>spanien all inclusive urlaub</t>
+          <t>urlaub spanien meer all inclusive mit flug</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії «все включено»</t>
+          <t>відпочинок на морі в Іспанії «все включено» з перельотом</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>1600</v>
+        <v>390</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (4/7). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (3/7). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
         </is>
       </c>
     </row>
@@ -7820,23 +7820,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>spanien urlaub all inclusive mit flug 2026</t>
+          <t>spanien urlaub günstig all inclusive</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії «все включено» з перельотом 2026</t>
+          <t>недорогий відпочинок в Іспанії «все включено»</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>all inclusive (регіон)</t>
+          <t>all inclusive (країна)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>2/9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (4/7). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (3/9). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
         </is>
       </c>
     </row>
@@ -7882,27 +7882,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>urlaub spanien meer all inclusive mit flug</t>
+          <t>spanien urlaub mit flug und hotel all inclusive</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>відпочинок на морі в Іспанії «все включено» з перельотом</t>
+          <t>відпочинок в Іспанії з перельотом і готелем «все включено»</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>390</v>
+        <v>170</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7922,17 +7922,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>спірно → підтверджено перевіркою</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (3/7). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -7944,23 +7944,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>spanien urlaub günstig all inclusive</t>
+          <t>spanien urlaub günstig all inclusive mit flug</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>недорогий відпочинок в Іспанії «все включено»</t>
+          <t>недорогий відпочинок в Іспанії «все включено» з перельотом</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -8006,27 +8006,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>spanien urlaub mit flug und hotel all inclusive</t>
+          <t>urlaub spanien festland all inclusive</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії з перельотом і готелем «все включено»</t>
+          <t>відпочинок у материковій Іспанії «все включено»</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -8046,17 +8046,17 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (5/9)</t>
         </is>
       </c>
     </row>
@@ -8068,23 +8068,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>spanien urlaub günstig all inclusive mit flug</t>
+          <t>spanien festland all inclusive</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>недорогий відпочинок в Іспанії «все включено» з перельотом</t>
+          <t>материкова Іспанія «все включено»</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.85</v>
+        <v>1.01</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -8108,45 +8108,45 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>спірно → підтверджено перевіркою</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (3/9). 4 домени (lidl-reisen, tui, sonnenklar.tv, ab-ins-blaue) мають і хаб Spanien, і окрему сторінку Spanien All Inclusive: різні H1, збіг тексту 0.00–0.02</t>
+          <t>найкращий кандидат: /tour/spanien/all-inclusive (5/9)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>K03 · spanien all inclusive urlaub</t>
+          <t>K04 · hotels spanien</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>urlaub spanien festland all inclusive</t>
+          <t>hotels spanien</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>відпочинок у материковій Іспанії «все включено»</t>
+          <t>готелі Іспанії</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>70</v>
+        <v>2400</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8</v>
+        <v>0.949999988079071</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -8160,55 +8160,55 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/all-inclusive</t>
+          <t>https://reisemu.de/hotels/spanien</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>all inclusive (країна)</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (5/9)</t>
+          <t>найкращий кандидат: /tour/spanien (2/7). Правило скіла: ключі зі словами Hotel/Hotels/Unterkunft/Unterkünfte без регіону й без іншого типу туру ведуть на сторінку готелів (hotels_page напрямку). У ТОП hotel-сторінок 2/7; за ТОП було б: /tour/spanien (окрема сторінка не потрібна).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>K03 · spanien all inclusive urlaub</t>
+          <t>K04 · hotels spanien</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>spanien festland all inclusive</t>
+          <t>hotels spanien festland</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>материкова Іспанія «все включено»</t>
+          <t>готелі материкової Іспанії</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1.01</v>
+        <v>0.49</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -8222,17 +8222,17 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/all-inclusive</t>
+          <t>https://reisemu.de/hotels/spanien</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>all inclusive (країна)</t>
+          <t>готель</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -8242,35 +8242,35 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/all-inclusive (5/9)</t>
+          <t>найкращий кандидат: /hotels/spanien (5/7)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>K04a · hotels spanien</t>
+          <t>K05a · spanien reise</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>hotels spanien</t>
+          <t>spanien reise</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>готелі Іспанії</t>
+          <t>подорож до Іспанії</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>2400</v>
+        <v>880</v>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.949999988079071</v>
+        <v>1.03</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -8289,22 +8289,22 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (2/7)</t>
+          <t>найкращий кандидат: /tour/spanien (5/8)</t>
         </is>
       </c>
     </row>
@@ -8316,15 +8316,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>spanien reise</t>
+          <t>spanien reiseziele</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>подорож до Іспанії</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
+          <t>куди поїхати в Іспанії</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Reiseziele — туристичні напрямки всередині країни</t>
+        </is>
+      </c>
       <c r="E61" t="n">
         <v>880</v>
       </c>
@@ -8332,11 +8336,11 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.03</v>
+        <v>0.8899999856948853</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8351,22 +8355,22 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>окрема сторінка не потрібна</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (5/8)</t>
+          <t>найкращий кандидат: /tour/spanien (1/8)</t>
         </is>
       </c>
     </row>
@@ -8378,27 +8382,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>spanien reiseziele</t>
+          <t>kann man mit aufenthaltstitel nach spanien reisen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>куди поїхати в Іспанії</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Reiseziele — туристичні напрямки всередині країни</t>
-        </is>
-      </c>
+          <t>чи можна їхати до Іспанії з посвідкою на проживання</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>880</v>
+        <v>70</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0.8899999856948853</v>
+        <v>3</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -8417,22 +8414,22 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (1/8)</t>
+          <t>найкращий кандидат: /tour/spanien/ratgeber (7/9). /ratgeber не створюємо: ключ на хаб (FAQ) За ТОП було б: /tour/spanien/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -8444,24 +8441,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kann man mit aufenthaltstitel nach spanien reisen</t>
+          <t>reise buchen spanien</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>чи можна їхати до Іспанії з посвідкою на проживання</t>
+          <t>забронювати подорож до Іспанії</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1.41</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>за рішенням власника</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/ratgeber (7/9). /ratgeber не створюємо: ключ на хаб (FAQ) За ТОП було б: /tour/spanien/ratgeber (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/spanien (7/9)</t>
         </is>
       </c>
     </row>
@@ -8503,12 +8503,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>reise buchen spanien</t>
+          <t>reise nach spanien mit bus</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>забронювати подорож до Іспанії</t>
+          <t>подорож до Іспанії автобусом</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -8519,7 +8519,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>1.41</v>
+        <v>0.61</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -8538,22 +8538,22 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>rundreise</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (7/9)</t>
+          <t>найкращий кандидат: /tour/spanien/rundreisen (3/8)</t>
         </is>
       </c>
     </row>
@@ -8565,12 +8565,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>reise nach spanien mit bus</t>
+          <t>reisen mit dem bus nach spanien</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>подорож до Іспанії автобусом</t>
+          <t>поїздки автобусом до Іспанії</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -8585,7 +8585,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>rundreise</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -8615,39 +8615,39 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/rundreisen (3/8)</t>
+          <t>найкращий кандидат: /tour/spanien (3/9)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>K05a · spanien reise</t>
+          <t>K06 · günstiger urlaub spanien</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>reisen mit dem bus nach spanien</t>
+          <t>günstiger urlaub spanien</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>поїздки автобусом до Іспанії</t>
+          <t>недорогий відпочинок в Іспанії</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>50</v>
+        <v>720</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G66" t="n">
-        <v>0.61</v>
+        <v>1.15</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -8672,12 +8672,12 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (3/9)</t>
+          <t>найкращий кандидат: /tour/spanien/last-minute (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -8689,23 +8689,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>günstiger urlaub spanien</t>
+          <t>billig urlaub spanien</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>недорогий відпочинок в Іспанії</t>
+          <t>дешевий відпочинок в Іспанії</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>720</v>
+        <v>170</v>
       </c>
       <c r="F67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>last minute (країна)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/last-minute (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien/last-minute (3/9)</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>billig urlaub spanien</t>
+          <t>billige urlaub spanien</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8759,7 +8759,11 @@
           <t>дешевий відпочинок в Іспанії</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>граматично неправильна форма</t>
+        </is>
+      </c>
       <c r="E68" t="n">
         <v>170</v>
       </c>
@@ -8767,7 +8771,7 @@
         <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>1.16</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -8786,22 +8790,22 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>last minute (країна)</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/last-minute (3/9)</t>
+          <t>найкращий кандидат: /tour/spanien (8/9)</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8817,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>billige urlaub spanien</t>
+          <t>billiger urlaub spanien</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8821,11 +8825,7 @@
           <t>дешевий відпочинок в Іспанії</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>граматично неправильна форма</t>
-        </is>
-      </c>
+      <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" t="n">
         <v>170</v>
       </c>
@@ -8879,23 +8879,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>billiger urlaub spanien</t>
+          <t>spanien reise günstig</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>дешевий відпочинок в Іспанії</t>
+          <t>недорога подорож до Іспанії</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="F70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>1.159999966621399</v>
+        <v>0.99</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -8941,27 +8941,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>spanien reise günstig</t>
+          <t>urlaub spanien günstig buchen</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>недорога подорож до Іспанії</t>
+          <t>недорого забронювати відпочинок в Іспанії</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" t="n">
         <v>50</v>
       </c>
-      <c r="F71" t="n">
-        <v>0</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
       </c>
       <c r="G71" t="n">
-        <v>0.99</v>
+        <v>1.17</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -8981,7 +8983,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -8991,37 +8993,35 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (8/9)</t>
+          <t>найкращий кандидат: /tour/spanien (7/9)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>K06 · günstiger urlaub spanien</t>
+          <t>K01b · spanien unterkunft</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>urlaub spanien günstig buchen</t>
+          <t>spanien unterkunft</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>недорого забронювати відпочинок в Іспанії</t>
+          <t>житло в Іспанії</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>50</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+        <v>320</v>
+      </c>
+      <c r="F72" t="n">
+        <v>22</v>
       </c>
       <c r="G72" t="n">
-        <v>1.17</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien</t>
+          <t>https://reisemu.de/hotels/spanien</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9045,34 +9045,34 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (7/9)</t>
+          <t>найкращий кандидат: /tour/spanien (4/7). Правило скіла: ключі зі словами Hotel/Hotels/Unterkunft/Unterkünfte без регіону й без іншого типу туру ведуть на сторінку готелів (hotels_page напрямку). У ТОП hotel-сторінок 0/7; за ТОП було б: /tour/spanien (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>K07 · urlaub spanien malaga</t>
+          <t>K01b · spanien unterkunft</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>urlaub spanien malaga</t>
+          <t>unterkünfte spanien</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>відпочинок у Малазі, Іспанія</t>
+          <t>варіанти житла в Іспанії</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -9080,10 +9080,10 @@
         <v>320</v>
       </c>
       <c r="F73" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G73" t="n">
-        <v>0.86</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -9097,59 +9097,63 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/malaga</t>
+          <t>https://reisemu.de/hotels/spanien</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/malaga (7/9)</t>
+          <t>найкращий кандидат: /tour/spanien (2/7). Правило скіла: ключі зі словами Hotel/Hotels/Unterkunft/Unterkünfte без регіону й без іншого типу туру ведуть на сторінку готелів (hotels_page напрямку). У ТОП hotel-сторінок 0/7; за ТОП було б: /tour/spanien (окрема сторінка не потрібна).</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>K07 · urlaub spanien malaga</t>
+          <t>K01b · spanien unterkunft</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>málaga spanien urlaub</t>
+          <t>riu hotel spanien festland</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>відпочинок у Малазі, Іспанія</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
+          <t>готель RIU в материковій Іспанії</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>бренд готельної мережі</t>
+        </is>
+      </c>
       <c r="E74" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.86</v>
+        <v>3.08</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>навігаційний</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9159,17 +9163,17 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/malaga</t>
+          <t>https://reisemu.de/hotels/spanien</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>готель</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -9179,40 +9183,39 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/malaga (7/9)</t>
+          <t>найкращий кандидат: /hotels/spanien (9/9)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>K08 · einreise spanien</t>
+          <t>K07 · urlaub spanien malaga</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>einreise spanien</t>
+          <t>urlaub spanien malaga</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>в’їзд до Іспанії</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>правила в’їзду, документи</t>
-        </is>
-      </c>
+          <t>відпочинок у Малазі, Іспанія</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>590</v>
+        <v>320</v>
       </c>
       <c r="F75" t="n">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.86</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9222,59 +9225,59 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/reisehinweise</t>
+          <t>https://reisemu.de/tour/spanien/malaga</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/reisehinweise (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien/malaga (7/9)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>K05b · reisen nach südspanien</t>
+          <t>K07 · urlaub spanien malaga</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>reisen nach südspanien</t>
+          <t>málaga spanien urlaub</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>подорожі на південь Іспанії</t>
+          <t>відпочинок у Малазі, Іспанія</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1.139999985694885</v>
+        <v>0.86</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9284,17 +9287,17 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/rundreisen</t>
+          <t>https://reisemu.de/tour/spanien/malaga</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>rundreise</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -9304,39 +9307,40 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/rundreisen (6/9)</t>
+          <t>найкращий кандидат: /tour/spanien/malaga (7/9)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>K09 · spanien urlaub last minute</t>
+          <t>K08 · einreise spanien</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>spanien urlaub last minute</t>
+          <t>einreise spanien</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>гарячі тури до Іспанії</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
+          <t>в’їзд до Іспанії</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>правила в’їзду, документи</t>
+        </is>
+      </c>
       <c r="E77" t="n">
-        <v>390</v>
+        <v>590</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1.37</v>
+        <v>9</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9346,59 +9350,59 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/last-minute</t>
+          <t>https://reisemu.de/tour/spanien/reisehinweise</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>last minute (країна)</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/last-minute (6/9)</t>
+          <t>найкращий кандидат: /tour/spanien/reisehinweise (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>K10 · alicante spanien urlaub</t>
+          <t>K05b · reisen nach südspanien</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>alicante spanien urlaub</t>
+          <t>reisen nach südspanien</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>відпочинок в Аліканте, Іспанія</t>
+          <t>подорожі на південь Іспанії</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.74</v>
+        <v>1.139999985694885</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9408,55 +9412,55 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/alicante</t>
+          <t>https://reisemu.de/tour/spanien/rundreisen</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>rundreise</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/alicante (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/spanien/rundreisen (6/9)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>K11 · spanien mallorca urlaub</t>
+          <t>K09 · spanien urlaub last minute</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>spanien mallorca urlaub</t>
+          <t>spanien urlaub last minute</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>відпочинок на Майорці, Іспанія</t>
+          <t>гарячі тури до Іспанії</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="F79" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.98</v>
+        <v>1.37</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -9470,17 +9474,17 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/mallorca</t>
+          <t>https://reisemu.de/tour/spanien/last-minute</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>last minute (країна)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9490,35 +9494,35 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/mallorca (6/8)</t>
+          <t>найкращий кандидат: /tour/spanien/last-minute (6/9)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>K12 · urlaub spanien valencia</t>
+          <t>K10 · alicante spanien urlaub</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>urlaub spanien valencia</t>
+          <t>alicante spanien urlaub</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>відпочинок у Валенсії, Іспанія</t>
+          <t>відпочинок в Аліканте, Іспанія</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -9532,7 +9536,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/valencia</t>
+          <t>https://reisemu.de/tour/spanien/alicante</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -9542,45 +9546,45 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/valencia (6/9)</t>
+          <t>найкращий кандидат: /tour/spanien/alicante (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>K12 · urlaub spanien valencia</t>
+          <t>K11 · spanien mallorca urlaub</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>pauschalreise valencia spanien</t>
+          <t>spanien mallorca urlaub</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>пакетний тур до Валенсії, Іспанія</t>
+          <t>відпочинок на Майорці, Іспанія</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G81" t="n">
-        <v>1.43</v>
+        <v>0.98</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -9594,55 +9598,55 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/valencia</t>
+          <t>https://reisemu.de/tour/spanien/mallorca</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>pauschalreise (регіон)</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>за рішенням власника</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/valencia/pauschalreise (6/9). окрему сторінку /valencia/pauschalreise не створюємо: наявна сторінка регіону За ТОП було б: /tour/spanien/valencia/pauschalreise (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/spanien/mallorca (6/8)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>K13 · spanien andalusien urlaub</t>
+          <t>K12 · urlaub spanien valencia</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>spanien andalusien urlaub</t>
+          <t>urlaub spanien valencia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>відпочинок в Андалусії, Іспанія</t>
+          <t>відпочинок у Валенсії, Іспанія</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -9656,55 +9660,55 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/andalusien</t>
+          <t>https://reisemu.de/tour/spanien/valencia</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>rundreise</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/rundreisen (3/8)</t>
+          <t>найкращий кандидат: /tour/spanien/valencia (6/9)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>K14 · spanien barcelona urlaub</t>
+          <t>K12 · urlaub spanien valencia</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>spanien barcelona urlaub</t>
+          <t>pauschalreise valencia spanien</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>відпочинок у Барселоні, Іспанія</t>
+          <t>пакетний тур до Валенсії, Іспанія</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.82</v>
+        <v>1.43</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -9718,59 +9722,59 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/barcelona</t>
+          <t>https://reisemu.de/tour/spanien/valencia</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>pauschalreise (регіон)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien/barcelona (8/10)</t>
+          <t>найкращий кандидат: /tour/spanien/valencia/pauschalreise (6/9). окрему сторінку /valencia/pauschalreise не створюємо: наявна сторінка регіону За ТОП було б: /tour/spanien/valencia/pauschalreise (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>K15 · spanien oktober urlaub</t>
+          <t>K13 · spanien andalusien urlaub</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>spanien oktober urlaub</t>
+          <t>spanien andalusien urlaub</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії в жовтні</t>
+          <t>відпочинок в Андалусії, Іспанія</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="F84" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9780,63 +9784,59 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/spanien/october</t>
+          <t>https://reisemu.de/tour/spanien/andalusien</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>rundreise</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор)</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/spanien (4/8). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/spanien (спірно (не перевірено)).</t>
+          <t>найкращий кандидат: /tour/spanien/rundreisen (3/8)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>K01b · riu hotel spanien festland</t>
+          <t>K14 · spanien barcelona urlaub</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>riu hotel spanien festland</t>
+          <t>spanien barcelona urlaub</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>готель RIU в материковій Іспанії</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>бренд готельної мережі</t>
-        </is>
-      </c>
+          <t>відпочинок у Барселоні, Іспанія</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
-        <v>3.08</v>
+        <v>0.82</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>навігаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9846,17 +9846,17 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://reisemu.de/hotels/spanien</t>
+          <t>https://reisemu.de/tour/spanien/barcelona</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>готель</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -9866,39 +9866,39 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /hotels/spanien (9/9)</t>
+          <t>найкращий кандидат: /tour/spanien/barcelona (8/10)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>K04b · hotels spanien festland</t>
+          <t>K15 · spanien oktober urlaub</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>hotels spanien festland</t>
+          <t>spanien oktober urlaub</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>готелі материкової Іспанії</t>
+          <t>відпочинок в Іспанії в жовтні</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G86" t="n">
-        <v>0.49</v>
+        <v>0.89</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9908,27 +9908,27 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://reisemu.de/hotels/spanien</t>
+          <t>https://reisemu.de/tour/spanien/october</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>готель</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>4/8</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>наявна посадкова (модифікатор)</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /hotels/spanien (5/7)</t>
+          <t>найкращий кандидат: /tour/spanien (4/8). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/spanien (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32670</v>
+        <v>32030</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -10126,17 +10126,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>131/365</t>
+          <t>123/351</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 8, окрема сторінка не потрібна: 9, спірно (не перевірено): 18, спірно (SERP не підтверджено): 7, за рішенням власника: 1</t>
+          <t>рекомендовано: 8, окрема сторінка не потрібна: 8, спірно (не перевірено): 17, спірно (SERP не підтверджено): 7, за рішенням власника: 1</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K04a · hotels spanien</t>
+          <t>K04 · hotels spanien</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10273,10 +10273,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2400</v>
+        <v>2470</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien. Хаб країни «Spanien»: у ТОП домінують хаби країни. Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>ІСНУЄ → /hotels/spanien. Хаб готелів.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -10295,22 +10295,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>готель</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>7/14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна: 1</t>
+          <t>за бізнес-правилом: 1, рекомендовано: 1</t>
         </is>
       </c>
     </row>
@@ -10433,137 +10433,137 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K07 · urlaub spanien malaga</t>
+          <t>K01b · spanien unterkunft</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>urlaub spanien malaga</t>
+          <t>spanien unterkunft</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>відпочинок у Малазі, Іспанія</t>
+          <t>житло в Іспанії</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>640</v>
+        <v>730</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien/malaga. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /hotels/spanien. Хаб готелів. Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Malaga</t>
+          <t>Spanien Urlaub: бронювання, рік, з перельотом</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 2</t>
+          <t>за бізнес-правилом: 2, рекомендовано: 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K08 · einreise spanien</t>
+          <t>K07 · urlaub spanien malaga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>einreise spanien</t>
+          <t>urlaub spanien malaga</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>в’їзд до Іспанії</t>
+          <t>відпочинок у Малазі, Іспанія</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>590</v>
+        <v>640</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/spanien/reisehinweise. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
+          <t>ІСНУЄ → /tour/spanien/malaga. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Spanien: Einreise, Personalausweis, Visum, Impfung</t>
+          <t>Регіон: Malaga</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>13/18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено): 1</t>
+          <t>рекомендовано: 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K05b · reisen nach südspanien</t>
+          <t>K08 · einreise spanien</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>reisen nach südspanien</t>
+          <t>einreise spanien</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>подорожі на південь Іспанії</t>
+          <t>в’їзд до Іспанії</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>390</v>
+        <v>590</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -10575,49 +10575,49 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/spanien/rundreisen. Rundreise — інший продукт (тури з маршрутом). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>НОВА → /tour/spanien/reisehinweise. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Spanien Reise / Reisen: buchen, nach</t>
+          <t>Spanien: Einreise, Personalausweis, Visum, Impfung</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>rundreise</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 1</t>
+          <t>спірно (SERP не підтверджено): 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K09 · spanien urlaub last minute</t>
+          <t>K05b · reisen nach südspanien</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>spanien urlaub last minute</t>
+          <t>reisen nach südspanien</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>гарячі тури до Іспанії</t>
+          <t>подорожі на південь Іспанії</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10628,22 +10628,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/spanien/last-minute. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>НОВА → /tour/spanien/rundreisen. Rundreise — інший продукт (тури з маршрутом). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Last Minute Spanien</t>
+          <t>Spanien Reise / Reisen: buchen, nach</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>last minute (країна)</t>
+          <t>rundreise</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -10665,21 +10665,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K10 · alicante spanien urlaub</t>
+          <t>K09 · spanien urlaub last minute</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>alicante spanien urlaub</t>
+          <t>spanien urlaub last minute</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>відпочинок в Аліканте, Іспанія</t>
+          <t>гарячі тури до Іспанії</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>260</v>
+        <v>390</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -10691,49 +10691,49 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien/alicante. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>НОВА → /tour/spanien/last-minute. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Alicante</t>
+          <t>Last Minute Spanien</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>last minute (країна)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено): 1</t>
+          <t>рекомендовано: 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K11 · spanien mallorca urlaub</t>
+          <t>K10 · alicante spanien urlaub</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>spanien mallorca urlaub</t>
+          <t>alicante spanien urlaub</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>відпочинок на Майорці, Іспанія</t>
+          <t>відпочинок в Аліканте, Іспанія</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien/mallorca. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /tour/spanien/alicante. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Mallorca</t>
+          <t>Регіон: Alicante</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10764,41 +10764,41 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 1</t>
+          <t>спірно (SERP не підтверджено): 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K12 · urlaub spanien valencia</t>
+          <t>K11 · spanien mallorca urlaub</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>urlaub spanien valencia</t>
+          <t>spanien mallorca urlaub</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>відпочинок у Валенсії, Іспанія</t>
+          <t>відпочинок на Майорці, Іспанія</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -10807,12 +10807,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien/valencia. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /tour/spanien/mallorca. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Valencia</t>
+          <t>Регіон: Mallorca</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10822,41 +10822,41 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 1, за рішенням власника: 1</t>
+          <t>рекомендовано: 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K13 · spanien andalusien urlaub</t>
+          <t>K12 · urlaub spanien valencia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>spanien andalusien urlaub</t>
+          <t>urlaub spanien valencia</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>відпочинок в Андалусії, Іспанія</t>
+          <t>відпочинок у Валенсії, Іспанія</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -10865,49 +10865,49 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien/andalusien. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /tour/spanien/valencia. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Andalusien</t>
+          <t>Регіон: Valencia</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>rundreise</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>9/18</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>спірно (не перевірено): 1</t>
+          <t>рекомендовано: 1, за рішенням власника: 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K14 · spanien barcelona urlaub</t>
+          <t>K13 · spanien andalusien urlaub</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>spanien barcelona urlaub</t>
+          <t>spanien andalusien urlaub</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>відпочинок у Барселоні, Іспанія</t>
+          <t>відпочинок в Андалусії, Іспанія</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10923,165 +10923,165 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien/barcelona. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /tour/spanien/andalusien. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Barcelona</t>
+          <t>Регіон: Andalusien</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>rundreise</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8/10</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 1</t>
+          <t>спірно (не перевірено): 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K15 · spanien oktober urlaub</t>
+          <t>K14 · spanien barcelona urlaub</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>spanien oktober urlaub</t>
+          <t>spanien barcelona urlaub</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>відпочинок в Іспанії в жовтні</t>
+          <t>відпочинок у Барселоні, Іспанія</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/spanien/october. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
+          <t>ІСНУЄ → /tour/spanien/barcelona. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Spanien Urlaub за місяцями</t>
+          <t>Регіон: Barcelona</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>8/10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор): 1</t>
+          <t>рекомендовано: 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K01b · riu hotel spanien festland</t>
+          <t>K15 · spanien oktober urlaub</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>riu hotel spanien festland</t>
+          <t>spanien oktober urlaub</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>готель RIU в материковій Іспанії</t>
+          <t>відпочинок в Іспанії в жовтні</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>навігаційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /hotels/spanien. Хаб готелів. Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>ІСНУЄ → /tour/spanien/october. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Spanien Urlaub: бронювання, рік, з перельотом</t>
+          <t>Spanien Urlaub за місяцями</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>готель</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>4/8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 1</t>
+          <t>наявна посадкова (модифікатор): 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K04b · hotels spanien festland</t>
+          <t>K16 · spanien urlaub gefährlich</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hotels spanien festland</t>
+          <t>spanien urlaub gefährlich</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>готелі материкової Іспанії</t>
+          <t>чи небезпечно відпочивати в Іспанії</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -11092,32 +11092,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /hotels/spanien. Хаб готелів. Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>НОВА → /tour/spanien/reisehinweise. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Hotels Spanien</t>
+          <t>Spanien: Reisewarnung, Sicherheit, Auswärtiges Amt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>готель</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11126,66 +11126,8 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>K16 · spanien urlaub gefährlich</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>spanien urlaub gefährlich</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>чи небезпечно відпочивати в Іспанії</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>70</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>інформаційний</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>НОВА → /tour/spanien/reisehinweise. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Spanien: Reisewarnung, Sicherheit, Auswärtiges Amt</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>інформаційна</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>8/9</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>рекомендовано: 1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L20"/>
+  <autoFilter ref="A1:L19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34785,7 +34727,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
     </row>
@@ -37029,7 +36971,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
     </row>
@@ -37097,7 +37039,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>окрема сторінка не потрібна</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
     </row>
@@ -40556,7 +40498,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>/hotels/spanien (2); /tour/spanien (1)</t>
+          <t>/hotels/spanien (3)</t>
         </is>
       </c>
     </row>
